--- a/Luban/Config/Datas/#HeroConfig.xlsx
+++ b/Luban/Config/Datas/#HeroConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D26DD5-9D77-4277-BFC2-CC8E8EDDBA61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B56BA6F-BB60-45AF-B3FA-28DB3E4932A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4770" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="1320" yWindow="6330" windowWidth="35565" windowHeight="9315" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,15 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>

--- a/Luban/Config/Datas/#HeroConfig.xlsx
+++ b/Luban/Config/Datas/#HeroConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B56BA6F-BB60-45AF-B3FA-28DB3E4932A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59EEF005-AF4A-4654-B6CA-A6C44A4E74B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1320" yWindow="6330" windowWidth="35565" windowHeight="9315" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{53B3FBB6-B116-408D-BCC0-737AAAC6C9D0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
